--- a/Supplemental_data/Supplemental data 16.xlsx
+++ b/Supplemental_data/Supplemental data 16.xlsx
@@ -19,7 +19,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="58">
   <si>
-    <t>Shared DEDMGs with opposite direction of expression change but the same hyper- or hypomethylation patterns between  regions and contexts of ecotypes</t>
+    <t>Shared differentially expressed differentially methylated genes exhibiting different regulation patterns between ecotypes and similar methylation patterns in the same region and context.</t>
   </si>
   <si>
     <t>Expression data for each ecotype follows the same order as the ecotype positions in column A</t>
